--- a/output/pdf_financials_xlsx/DWS.xlsx
+++ b/output/pdf_financials_xlsx/DWS.xlsx
@@ -5860,13 +5860,13 @@
         </is>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.128863</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0.15462</v>
+        <v>0.283483</v>
       </c>
       <c r="F92" s="3" t="n">
         <v>0.731272</v>
@@ -23538,7 +23538,11 @@
           <t>Reserve for warrants (Note 19(c))</t>
         </is>
       </c>
-      <c r="D175" t="inlineStr"/>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E175" t="inlineStr">
         <is>
           <t>-</t>
@@ -25958,7 +25962,11 @@
           <t>Reserve for warrants (Note 17(c))</t>
         </is>
       </c>
-      <c r="D203" t="inlineStr"/>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E203" t="inlineStr">
         <is>
           <t>-</t>
@@ -27598,7 +27606,11 @@
           <t>Reserves (note 4 and 5)</t>
         </is>
       </c>
-      <c r="D222" t="inlineStr"/>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E222" t="inlineStr">
         <is>
           <t>-</t>
